--- a/documentation/example_surveys/data_quality.xlsx
+++ b/documentation/example_surveys/data_quality.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>type</t>
   </si>
@@ -93,6 +93,24 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>server HTTP_SEC_CH_UA_PLATFORM</t>
+  </si>
+  <si>
+    <t>dq_ch_platform</t>
+  </si>
+  <si>
+    <t>server HTTP_SEC_CH_UA_MOBILE</t>
+  </si>
+  <si>
+    <t>dq_ch_mobile</t>
+  </si>
+  <si>
+    <t>server HTTP_SIGNATURE_AGENT</t>
+  </si>
+  <si>
+    <t>dq_sig_agent</t>
   </si>
   <si>
     <t>weekend_rested</t>
@@ -525,7 +543,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -615,199 +633,232 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
+      <c r="D6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="L7" t="s">
         <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8">
-        <v>3</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" t="s">
         <v>43</v>
       </c>
-      <c r="I13" t="s">
-        <v>44</v>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
+      <c r="D14" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
         <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +887,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>

--- a/documentation/example_surveys/data_quality.xlsx
+++ b/documentation/example_surveys/data_quality.xlsx
@@ -62,7 +62,7 @@
   <si>
     <t>## Before you start
 This short example study asks about your last weekend.
-To check data quality, we record on each page, as counts, durations and yes/no values only: time on the page; how often and how long you leave it; copy and paste counts and lengths; numbers of key presses, corrections, clicks, scrolls and mouse or touch movements; a few summary values about typing rhythm and click timing; whether text or answers appear without key presses or clicks; basic browser information (browser family, mobile or desktop, mouse or touchscreen, whether the browser reports being remote-controlled, whether its actual engine and version match what it reports, which systems for protected video (DRM) it supports, whether automation tools or AI writing assistants leave traces on the page, one yes/no value for accessibility settings); and the browser identification your browser sends. We do not store your IP address, a device fingerprint, what you type key by key, your mouse path or the content of your clipboard. This information is deleted six months after data collection ends at the latest. Please answer on your own and do not use AI tools such as ChatGPT to answer the questions. Each page also contains a short note and a field addressed to automated tools that are not shown on screen; if you use a screen reader, please skip them.</t>
+To check data quality, we record on each page, as counts, durations and yes/no values only: time on the page; how often and how long you leave it; copy and paste counts and lengths; numbers of key presses, corrections, clicks, scrolls and mouse or touch movements; a few summary values about typing rhythm and click timing; whether text or answers appear without key presses or clicks; basic browser information (browser family, mobile or desktop, mouse or touchscreen, whether the browser reports being remote-controlled, whether its window, screen, graphics, plugins and languages look like those of an automated browser, whether its actual engine and version match what it reports, which systems for protected video (DRM) it supports, whether automation tools or AI writing assistants leave traces on the page, one yes/no value for accessibility settings); and the browser identification your browser sends. We do not store your IP address, a device fingerprint, what you type key by key, your mouse path or the content of your clipboard. This information is deleted six months after data collection ends at the latest. Please answer on your own and do not use AI tools such as ChatGPT to answer the questions. Each page also contains a short note and a field addressed to automated tools that are not shown on screen; if you use a screen reader, please skip them.</t>
   </si>
   <si>
     <t>mc_button</t>
